--- a/Lab_4/data/partB/param_optimization_process/v150_k20_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k20_s200_results.xlsx
@@ -518,46 +518,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -573,13 +573,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -594,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,25 +677,25 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -704,19 +704,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -735,40 +735,40 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -790,19 +790,19 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -811,16 +811,16 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -830,25 +830,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
         <v>43</v>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -866,13 +866,13 @@
         <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -894,37 +894,37 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,19 +958,19 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,19 +998,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>24</v>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -1028,7 +1028,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,25 +1062,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>8</v>
@@ -1111,22 +1111,22 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1148,13 +1148,13 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>7</v>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -1175,16 +1175,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,25 +1215,25 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,43 +1246,43 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
         <v>4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
